--- a/data/trans_dic/P32B-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P32B-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se ha sentido mal o culpable por su forma de beber</t>
+          <t>Población que se ha sentido mal o culpable por su forma de beber (tasa de respuesta: 99,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,28</t>
+          <t>0,32; 3,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,33; 8,9</t>
+          <t>3,35; 8,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,88; 5,21</t>
+          <t>1,12; 5,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,51</t>
+          <t>0,0; 0,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 5,09</t>
+          <t>0,63; 5,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,09; 6,25</t>
+          <t>1,07; 6,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,55; 5,25</t>
+          <t>0,54; 4,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 13,36</t>
+          <t>0,16; 12,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,41</t>
+          <t>0,65; 3,07</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,89; 6,54</t>
+          <t>2,65; 6,3</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,13; 4,05</t>
+          <t>1,17; 3,98</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 5,38</t>
+          <t>0,12; 5,21</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,46</t>
+          <t>0,17; 1,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,72; 5,2</t>
+          <t>1,75; 5,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,89; 5,63</t>
+          <t>1,87; 5,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,55; 10,37</t>
+          <t>1,45; 10,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,83</t>
+          <t>0,0; 3,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,64</t>
+          <t>0,0; 2,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 4,67</t>
+          <t>0,83; 4,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,04</t>
+          <t>0,0; 3,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,48</t>
+          <t>0,26; 1,41</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,68</t>
+          <t>1,24; 3,77</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,7; 4,5</t>
+          <t>1,68; 4,43</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,1; 6,52</t>
+          <t>1,08; 6,09</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,57</t>
+          <t>0,0; 1,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,6; 4,96</t>
+          <t>1,5; 4,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,35</t>
+          <t>0,89; 3,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,12; 2,59</t>
+          <t>0,12; 3,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,3</t>
+          <t>0,0; 2,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,68</t>
+          <t>0,0; 1,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,49</t>
+          <t>0,0; 2,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,73</t>
+          <t>0,29; 3,68</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,33</t>
+          <t>0,14; 1,36</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,46</t>
+          <t>1,06; 3,44</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,56</t>
+          <t>0,71; 2,57</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,45</t>
+          <t>0,45; 2,36</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,65</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,26</t>
+          <t>0,54; 3,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,71</t>
+          <t>0,95; 4,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,81</t>
+          <t>0,3; 2,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,14</t>
+          <t>0,0; 4,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,92</t>
+          <t>0,0; 2,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,05</t>
+          <t>0,41; 3,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,29</t>
+          <t>0,0; 1,7</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,19</t>
+          <t>0,35; 2,17</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,2</t>
+          <t>0,86; 3,13</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,41</t>
+          <t>0,48; 2,42</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,37; 7,03</t>
+          <t>1,55; 7,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 5,45</t>
+          <t>0,36; 6,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,39; 4,91</t>
+          <t>0,64; 4,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,86; 6,26</t>
+          <t>1,71; 6,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,09</t>
+          <t>0,0; 9,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 5,39</t>
+          <t>1,13; 5,63</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,33; 6,12</t>
+          <t>1,16; 5,8</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 3,62</t>
+          <t>0,28; 3,58</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,26; 3,07</t>
+          <t>0,26; 3,05</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,97; 5,06</t>
+          <t>1,93; 5,02</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,43</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,64; 7,71</t>
+          <t>0,63; 7,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,75</t>
+          <t>0,0; 2,74</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,58</t>
+          <t>0,36; 3,17</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 5,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3,09</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,26</t>
+          <t>0,0; 1,22</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,45; 5,64</t>
+          <t>0,47; 6,18</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,62</t>
+          <t>0,0; 2,49</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,07; 1,66</t>
+          <t>0,08; 1,61</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,98</t>
+          <t>0,0; 6,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,42</t>
+          <t>0,0; 11,36</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,92</t>
+          <t>0,0; 4,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,54; 5,66</t>
+          <t>0,54; 5,29</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0; 8,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0; 7,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,18</t>
+          <t>0,0; 7,6</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,57</t>
+          <t>0,0; 6,32</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,25</t>
+          <t>0,0; 11,05</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,03</t>
+          <t>0,0; 2,97</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,13</t>
+          <t>0,46; 4,21</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,32</t>
+          <t>0,49; 1,31</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,13; 3,65</t>
+          <t>2,17; 3,78</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,53; 2,86</t>
+          <t>1,51; 2,93</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,32; 2,92</t>
+          <t>1,35; 3,07</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,82</t>
+          <t>0,51; 2,02</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,38</t>
+          <t>0,3; 1,38</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,68</t>
+          <t>0,57; 1,73</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,4</t>
+          <t>0,58; 2,31</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,28</t>
+          <t>0,59; 1,32</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,65; 2,73</t>
+          <t>1,61; 2,68</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,26</t>
+          <t>1,3; 2,2</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,35</t>
+          <t>1,13; 2,37</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se ha sentido mal o culpable por su forma de beber</t>
+          <t>Población que se ha sentido mal o culpable por su forma de beber (tasa de respuesta: 99,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>875; 9198</t>
+          <t>887; 10980</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9351; 24954</t>
+          <t>9411; 23833</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2264; 13364</t>
+          <t>2860; 13462</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 869</t>
+          <t>0; 818</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1178; 9483</t>
+          <t>1182; 9934</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1997; 11466</t>
+          <t>1972; 11238</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>937; 8967</t>
+          <t>928; 8093</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>169; 13473</t>
+          <t>163; 12804</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3261; 15937</t>
+          <t>3028; 14327</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13401; 30331</t>
+          <t>12291; 29250</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4843; 17299</t>
+          <t>4974; 17013</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>469; 14564</t>
+          <t>324; 14117</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>855; 7311</t>
+          <t>862; 7593</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8057; 24305</t>
+          <t>8190; 24710</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6926; 20599</t>
+          <t>6851; 21011</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3576; 23856</t>
+          <t>3326; 23923</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 6151</t>
+          <t>0; 7074</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 5635</t>
+          <t>0; 5108</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1895; 10542</t>
+          <t>1869; 9772</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4322</t>
+          <t>0; 4519</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1846; 10664</t>
+          <t>1850; 10159</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8687; 25053</t>
+          <t>8440; 25696</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10045; 26623</t>
+          <t>9938; 26209</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4078; 24263</t>
+          <t>4037; 22679</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6323</t>
+          <t>0; 6546</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6856; 21229</t>
+          <t>6410; 20752</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2998; 14484</t>
+          <t>3831; 15085</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>328; 7283</t>
+          <t>330; 9542</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5163</t>
+          <t>0; 4607</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4113</t>
+          <t>0; 4691</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 6191</t>
+          <t>0; 6257</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>438; 5599</t>
+          <t>440; 5527</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>876; 8296</t>
+          <t>865; 8486</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7587; 23241</t>
+          <t>7161; 23161</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4691; 17396</t>
+          <t>4845; 17484</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1912; 10572</t>
+          <t>1945; 10176</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2033</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2108; 12866</t>
+          <t>2147; 12524</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3812; 18322</t>
+          <t>3691; 17373</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1182; 9666</t>
+          <t>1044; 9713</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 6010</t>
+          <t>0; 5840</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 2178</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 7779</t>
+          <t>0; 7825</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>781; 5852</t>
+          <t>787; 5809</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 5901</t>
+          <t>0; 7816</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2604; 13290</t>
+          <t>2142; 13207</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5297; 20980</t>
+          <t>5607; 20496</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2689; 12899</t>
+          <t>2582; 12948</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2469; 12666</t>
+          <t>2799; 13974</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>832; 12641</t>
+          <t>839; 14369</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1125; 14082</t>
+          <t>1841; 12160</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4890; 16474</t>
+          <t>4495; 16329</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 5346</t>
+          <t>0; 7037</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 2150</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 2198</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1260; 7261</t>
+          <t>1521; 7582</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3407; 15630</t>
+          <t>2966; 14830</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>820; 12442</t>
+          <t>946; 12309</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1099; 12787</t>
+          <t>1099; 12708</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>7846; 20140</t>
+          <t>7696; 19969</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1858</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>983; 11906</t>
+          <t>976; 11832</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 4884</t>
+          <t>0; 4870</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>958; 6782</t>
+          <t>677; 6006</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 1752</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 2114</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 2087</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3520</t>
+          <t>0; 3418</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 1851</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>951; 11945</t>
+          <t>1003; 13101</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 3961</t>
+          <t>0; 6095</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>320; 7791</t>
+          <t>366; 7528</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 5108</t>
+          <t>0; 5062</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 10623</t>
+          <t>0; 9716</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 3737</t>
+          <t>0; 4557</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>544; 5663</t>
+          <t>544; 5289</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 2083</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 2015</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 2679</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 2176</t>
+          <t>0; 2021</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 4996</t>
+          <t>0; 5670</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0; 12360</t>
+          <t>0; 12142</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0; 4002</t>
+          <t>0; 3914</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>561; 5233</t>
+          <t>578; 5334</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>8534; 24749</t>
+          <t>9219; 24710</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>43502; 74590</t>
+          <t>44262; 77238</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>30624; 57266</t>
+          <t>30208; 58754</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>20826; 46118</t>
+          <t>21348; 48429</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>4061; 16261</t>
+          <t>4583; 18108</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3043; 14437</t>
+          <t>3117; 14522</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5964; 19275</t>
+          <t>6479; 19812</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>6984; 24659</t>
+          <t>5925; 23663</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>15956; 35383</t>
+          <t>16469; 36675</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>50990; 84477</t>
+          <t>49859; 82695</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>39831; 71195</t>
+          <t>40930; 69369</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>29953; 61236</t>
+          <t>29293; 61773</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P32B-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P32B-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,91</t>
+          <t>0,31; 3,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,35; 8,5</t>
+          <t>3,24; 8,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 5,25</t>
+          <t>0,88; 5,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,48</t>
+          <t>0,0; 5,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 5,33</t>
+          <t>0,63; 5,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,07; 6,12</t>
+          <t>1,14; 7,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 4,74</t>
+          <t>0,55; 5,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,16; 12,7</t>
+          <t>1,51; 14,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,07</t>
+          <t>0,72; 3,31</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,65; 6,3</t>
+          <t>2,81; 6,5</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,98</t>
+          <t>1,0; 3,91</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,12; 5,21</t>
+          <t>0,78; 6,36</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,52</t>
+          <t>0,17; 1,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,75; 5,28</t>
+          <t>1,73; 5,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,87; 5,75</t>
+          <t>1,91; 5,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,45; 10,4</t>
+          <t>1,75; 9,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,26</t>
+          <t>0,0; 3,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,39</t>
+          <t>0,0; 2,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 4,33</t>
+          <t>0,81; 4,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,18</t>
+          <t>0,0; 2,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,41</t>
+          <t>0,26; 1,45</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,77</t>
+          <t>1,36; 3,7</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,68; 4,43</t>
+          <t>1,7; 4,43</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,08; 6,09</t>
+          <t>1,21; 6,06</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,63</t>
+          <t>0,0; 1,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,5; 4,85</t>
+          <t>1,5; 4,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,49</t>
+          <t>0,89; 3,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,12; 3,39</t>
+          <t>0,37; 3,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,05</t>
+          <t>0,0; 2,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,92</t>
+          <t>0,0; 1,98</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,52</t>
+          <t>0,0; 2,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,68</t>
+          <t>0,27; 3,37</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,36</t>
+          <t>0,0; 1,23</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,44</t>
+          <t>1,09; 3,25</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,57</t>
+          <t>0,69; 2,51</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,36</t>
+          <t>0,59; 2,78</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -1142,22 +1142,22 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,18</t>
+          <t>0,55; 3,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,95; 4,47</t>
+          <t>0,99; 4,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,82</t>
+          <t>0,52; 3,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,02</t>
+          <t>0,0; 3,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1167,32 +1167,32 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,94</t>
+          <t>0,0; 2,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,03</t>
+          <t>0,57; 3,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,7</t>
+          <t>0,0; 1,51</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,17</t>
+          <t>0,48; 2,07</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,13</t>
+          <t>0,82; 3,06</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,42</t>
+          <t>0,65; 2,7</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -1277,27 +1277,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,55; 7,76</t>
+          <t>1,5; 8,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 6,2</t>
+          <t>0,35; 6,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,64; 4,24</t>
+          <t>0,39; 4,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,71; 6,21</t>
+          <t>1,66; 5,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,33</t>
+          <t>0,0; 5,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1312,27 +1312,27 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,13; 5,63</t>
+          <t>1,12; 5,3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,16; 5,8</t>
+          <t>1,41; 6,11</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 3,58</t>
+          <t>0,24; 4,38</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,26; 3,05</t>
+          <t>0,44; 2,84</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,93; 5,02</t>
+          <t>1,83; 4,85</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -1422,17 +1422,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,63; 7,66</t>
+          <t>0,63; 7,7</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,74</t>
+          <t>0,0; 2,95</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,17</t>
+          <t>0,53; 3,55</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,22</t>
+          <t>0,0; 3,44</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1462,17 +1462,17 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,47; 6,18</t>
+          <t>0,46; 5,82</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,49</t>
+          <t>0,0; 2,19</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,08; 1,61</t>
+          <t>0,52; 2,96</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -1557,22 +1557,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,92</t>
+          <t>0,0; 6,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,36</t>
+          <t>0,0; 13,35</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,78</t>
+          <t>0,0; 4,79</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,54; 5,29</t>
+          <t>0,5; 4,91</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1592,27 +1592,27 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,6</t>
+          <t>0,0; 7,45</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,32</t>
+          <t>0,0; 6,16</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,05</t>
+          <t>0,0; 10,1</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,97</t>
+          <t>0,0; 3,44</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,21</t>
+          <t>0,4; 4,28</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,31</t>
+          <t>0,45; 1,3</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,17; 3,78</t>
+          <t>2,06; 3,71</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,51; 2,93</t>
+          <t>1,56; 2,88</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,07</t>
+          <t>1,5; 3,18</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,02</t>
+          <t>0,55; 1,97</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,38</t>
+          <t>0,3; 1,41</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,73</t>
+          <t>0,54; 1,77</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,31</t>
+          <t>1,12; 3,32</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,32</t>
+          <t>0,6; 1,31</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,68</t>
+          <t>1,62; 2,73</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,3; 2,2</t>
+          <t>1,3; 2,21</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,37</t>
+          <t>1,55; 2,87</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>6178</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4166</t>
+          <t>7831</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>887; 10980</t>
+          <t>881; 9899</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9411; 23833</t>
+          <t>9093; 23817</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2860; 13462</t>
+          <t>2267; 13289</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 818</t>
+          <t>0; 8771</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1182; 9934</t>
+          <t>1180; 9587</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1972; 11238</t>
+          <t>2096; 13258</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>928; 8093</t>
+          <t>941; 8873</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>163; 12804</t>
+          <t>1699; 16308</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3028; 14327</t>
+          <t>3347; 15474</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12291; 29250</t>
+          <t>13024; 30163</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4974; 17013</t>
+          <t>4271; 16676</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>324; 14117</t>
+          <t>2167; 17749</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10469</t>
+          <t>10915</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>861</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11326</t>
+          <t>11776</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>862; 7593</t>
+          <t>866; 7711</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8190; 24710</t>
+          <t>8113; 25771</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6851; 21011</t>
+          <t>6990; 19750</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3326; 23923</t>
+          <t>4361; 23568</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 7074</t>
+          <t>0; 7233</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 5108</t>
+          <t>0; 5387</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1869; 9772</t>
+          <t>1826; 10425</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4519</t>
+          <t>0; 4458</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1850; 10159</t>
+          <t>1891; 10400</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8440; 25696</t>
+          <t>9266; 25225</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9938; 26209</t>
+          <t>10034; 26183</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4037; 22679</t>
+          <t>4850; 24392</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>4586</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>2087</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4576</t>
+          <t>6674</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6546</t>
+          <t>0; 6597</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6410; 20752</t>
+          <t>6419; 20867</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3831; 15085</t>
+          <t>3854; 14668</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>330; 9542</t>
+          <t>1143; 11495</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4607</t>
+          <t>0; 5497</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4691</t>
+          <t>0; 4831</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 6257</t>
+          <t>0; 6171</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>440; 5527</t>
+          <t>460; 5707</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>865; 8486</t>
+          <t>0; 7673</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7161; 23161</t>
+          <t>7318; 21867</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4845; 17484</t>
+          <t>4714; 17099</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1945; 10176</t>
+          <t>2826; 13377</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4087</t>
+          <t>4931</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3317</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6404</t>
+          <t>8248</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2147; 12524</t>
+          <t>2157; 13127</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3691; 17373</t>
+          <t>3866; 18189</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1044; 9713</t>
+          <t>1826; 11304</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 5840</t>
+          <t>0; 5786</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2722,32 +2722,32 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 7825</t>
+          <t>0; 7720</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>787; 5809</t>
+          <t>1202; 6918</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 7816</t>
+          <t>0; 6928</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2142; 13207</t>
+          <t>2932; 12545</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5607; 20496</t>
+          <t>5351; 20052</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2582; 12948</t>
+          <t>3663; 15284</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9266</t>
+          <t>9079</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3544</t>
+          <t>3813</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12810</t>
+          <t>12892</t>
         </is>
       </c>
     </row>
@@ -2900,27 +2900,27 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2799; 13974</t>
+          <t>2700; 14704</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>839; 14369</t>
+          <t>819; 14300</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1841; 12160</t>
+          <t>1110; 11896</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4495; 16329</t>
+          <t>4668; 16106</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 7037</t>
+          <t>0; 4206</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2935,27 +2935,27 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1521; 7582</t>
+          <t>1661; 7837</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2966; 14830</t>
+          <t>3597; 15621</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>946; 12309</t>
+          <t>818; 15066</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1099; 12708</t>
+          <t>1834; 11820</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>7696; 19969</t>
+          <t>7839; 20786</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2520</t>
+          <t>3286</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>457</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2970</t>
+          <t>3743</t>
         </is>
       </c>
     </row>
@@ -3113,17 +3113,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>976; 11832</t>
+          <t>974; 11890</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 4870</t>
+          <t>0; 5245</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>677; 6006</t>
+          <t>1104; 7356</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3418</t>
+          <t>0; 2739</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -3153,17 +3153,17 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1003; 13101</t>
+          <t>980; 12341</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 6095</t>
+          <t>0; 5361</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>366; 7528</t>
+          <t>1498; 8474</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1816</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>431</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>2220</t>
+          <t>2346</t>
         </is>
       </c>
     </row>
@@ -3316,22 +3316,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 5062</t>
+          <t>0; 5071</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 9716</t>
+          <t>0; 11417</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 4557</t>
+          <t>0; 4570</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>544; 5289</t>
+          <t>549; 5390</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3351,27 +3351,27 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 2021</t>
+          <t>0; 2245</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 5670</t>
+          <t>0; 5525</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0; 12142</t>
+          <t>0; 11099</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0; 3914</t>
+          <t>0; 4544</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>578; 5334</t>
+          <t>555; 5983</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>30947</t>
+          <t>36366</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>13525</t>
+          <t>17144</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>44472</t>
+          <t>53510</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>9219; 24710</t>
+          <t>8433; 24419</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>44262; 77238</t>
+          <t>42163; 75862</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>30208; 58754</t>
+          <t>31229; 57730</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>21348; 48429</t>
+          <t>25195; 53349</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>4583; 18108</t>
+          <t>4926; 17607</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3117; 14522</t>
+          <t>3102; 14773</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>6479; 19812</t>
+          <t>6212; 20315</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>5925; 23663</t>
+          <t>10156; 29995</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>16469; 36675</t>
+          <t>16605; 36431</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>49859; 82695</t>
+          <t>50203; 84351</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>40930; 69369</t>
+          <t>40959; 69605</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>29293; 61773</t>
+          <t>40166; 74234</t>
         </is>
       </c>
     </row>
